--- a/viewer/downloads/CCG_Alignment.xlsx
+++ b/viewer/downloads/CCG_Alignment.xlsx
@@ -62,7 +62,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +77,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -120,6 +125,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,9 +498,9 @@
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -602,15 +608,19 @@
           <t>9.2.4.12, 9.2.4.6</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr"/>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>7.RP.A.2.D, 7.SP.7a</t>
+        </is>
+      </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>9.2.4.12 (MN-2022), 9.2.4.6 (MN-2022)</t>
+          <t>7.RP.A.2.D (CCSS-M), 7.SP.7a (CCSS-M), 9.2.4.12 (MN-2022), 9.2.4.6 (MN-2022)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -633,15 +643,19 @@
           <t>9.2.4.1, 9.2.4.12, 9.2.4.13, 9.2.4.14</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.A, 7.SP.7a, 7.SP.7b, 7.SP.7c</t>
+        </is>
+      </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>9.2.4.1 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.13 (MN-2022), 9.2.4.14 (MN-2022)</t>
+          <t>7.NS.A.1.A (CCSS-M), 7.SP.7a (CCSS-M), 7.SP.7b (CCSS-M), 7.SP.7c (CCSS-M), 9.2.4.1 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.13 (MN-2022), 9.2.4.14 (MN-2022)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -677,15 +691,19 @@
           <t>9.2.4.1, 9.2.4.12, 9.2.4.7</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.A, 7.RP.A.2.B, 7.SP.7a</t>
+        </is>
+      </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>9.2.4.1 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.7 (MN-2022)</t>
+          <t>7.NS.A.1.A (CCSS-M), 7.RP.A.2.B (CCSS-M), 7.SP.7a (CCSS-M), 9.2.4.1 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.7 (MN-2022)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -708,15 +726,19 @@
           <t>9.2.3.6, 9.2.4.12</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr"/>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>5.NF.A.1, 7.SP.7a</t>
+        </is>
+      </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>9.2.3.6 (MN-2022), 9.2.4.12 (MN-2022)</t>
+          <t>5.NF.A.1 (CCSS-M), 7.SP.7a (CCSS-M), 9.2.3.6 (MN-2022), 9.2.4.12 (MN-2022)</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -752,15 +774,19 @@
           <t>9.2.3.9</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.D</t>
+        </is>
+      </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>9.2.3.9 (MN-2022)</t>
+          <t>7.NS.A.1.D (CCSS-M), 9.2.3.9 (MN-2022)</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -796,15 +822,19 @@
           <t>9.2.3.3, 9.2.3.8, 9.2.4.12</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>7.SP.7a, 7.SP.C.7.B, 7.SP.C.8.A</t>
+        </is>
+      </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>9.2.3.3 (MN-2022), 9.2.3.8 (MN-2022), 9.2.4.12 (MN-2022)</t>
+          <t>7.SP.7a (CCSS-M), 7.SP.C.7.B (CCSS-M), 7.SP.C.8.A (CCSS-M), 9.2.3.3 (MN-2022), 9.2.3.8 (MN-2022), 9.2.4.12 (MN-2022)</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -836,15 +866,19 @@
           <t>9.2.3.3, 9.2.3.8</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr"/>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>7.SP.C.7.B, 7.SP.C.8.A</t>
+        </is>
+      </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>9.2.3.3 (MN-2022), 9.2.3.8 (MN-2022)</t>
+          <t>7.SP.C.7.B (CCSS-M), 7.SP.C.8.A (CCSS-M), 9.2.3.3 (MN-2022), 9.2.3.8 (MN-2022)</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -863,15 +897,19 @@
           <t>9.1.2.8, 9.2.3.2, 9.2.3.3</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr"/>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>7.NS.A.2.D, 7.SP.C.7.B, 7.SP.C.8.C</t>
+        </is>
+      </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>9.1.2.8 (MN-2022), 9.2.3.2 (MN-2022), 9.2.3.3 (MN-2022)</t>
+          <t>7.NS.A.2.D (CCSS-M), 7.SP.C.7.B (CCSS-M), 7.SP.C.8.C (CCSS-M), 9.1.2.8 (MN-2022), 9.2.3.2 (MN-2022), 9.2.3.3 (MN-2022)</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -890,15 +928,19 @@
           <t>9.2.3.2, 9.2.3.3</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr"/>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>7.NS.A.2.D, 7.SP.C.7.B</t>
+        </is>
+      </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>9.2.3.2 (MN-2022), 9.2.3.3 (MN-2022)</t>
+          <t>7.NS.A.2.D (CCSS-M), 7.SP.C.7.B (CCSS-M), 9.2.3.2 (MN-2022), 9.2.3.3 (MN-2022)</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -930,15 +972,19 @@
           <t>9.2.4.10, 9.2.4.4, 9.2.4.5, 9.2.4.7</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr"/>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>7.NS.A.2.C, 7.RP.3, 7.RP.A.2.A, 7.RP.A.2.B</t>
+        </is>
+      </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>9.2.4.10 (MN-2022), 9.2.4.4 (MN-2022), 9.2.4.5 (MN-2022), 9.2.4.7 (MN-2022)</t>
+          <t>7.NS.A.2.C (CCSS-M), 7.RP.3 (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M), 9.2.4.10 (MN-2022), 9.2.4.4 (MN-2022), 9.2.4.5 (MN-2022), 9.2.4.7 (MN-2022)</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -957,15 +1003,19 @@
           <t>9.2.3.1, 9.2.4.10</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr"/>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>7.RP.3, 8.EE.C.7.B</t>
+        </is>
+      </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>9.2.3.1 (MN-2022), 9.2.4.10 (MN-2022)</t>
+          <t>7.RP.3 (CCSS-M), 8.EE.C.7.B (CCSS-M), 9.2.3.1 (MN-2022), 9.2.4.10 (MN-2022)</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1001,15 +1051,19 @@
           <t>9.1.2.1, 9.1.2.2, 9.1.2.3, 9.1.2.4, 9.1.2.7</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr"/>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>6.EE.A.2.C, 6.EE.A.4, 6.G.1, 6.RP.3c, Review skills needed for 6.NS.1</t>
+        </is>
+      </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>9.1.2.1 (MN-2022), 9.1.2.2 (MN-2022), 9.1.2.3 (MN-2022), 9.1.2.4 (MN-2022), 9.1.2.7 (MN-2022)</t>
+          <t>6.EE.A.2.C (CCSS-M), 6.EE.A.4 (CCSS-M), 6.G.1 (CCSS-M), 6.RP.3c (CCSS-M), 9.1.2.1 (MN-2022), 9.1.2.2 (MN-2022), 9.1.2.3 (MN-2022), 9.1.2.4 (MN-2022), 9.1.2.7 (MN-2022), Review skills needed for 6.NS.1 (CCSS-M)</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1028,15 +1082,19 @@
           <t>9.2.4.15</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr"/>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>7.SP.6</t>
+        </is>
+      </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>9.2.4.15 (MN-2022)</t>
+          <t>7.SP.6 (CCSS-M), 9.2.4.15 (MN-2022)</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1055,15 +1113,19 @@
           <t>9.2.4.3, 9.2.4.4, 9.2.4.7</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr"/>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>7.NS.A.2.A, 7.NS.A.2.C, 7.RP.A.2.B</t>
+        </is>
+      </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>9.2.4.3 (MN-2022), 9.2.4.4 (MN-2022), 9.2.4.7 (MN-2022)</t>
+          <t>7.NS.A.2.A (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.RP.A.2.B (CCSS-M), 9.2.4.3 (MN-2022), 9.2.4.4 (MN-2022), 9.2.4.7 (MN-2022)</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1082,15 +1144,19 @@
           <t>9.2.3.1</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr"/>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.B</t>
+        </is>
+      </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>9.2.3.1 (MN-2022)</t>
+          <t>8.EE.C.7.B (CCSS-M), 9.2.3.1 (MN-2022)</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1145,15 +1211,19 @@
           <t>9.2.4.10, 9.2.4.11, 9.2.4.12, 9.2.4.4, 9.2.4.6, 9.2.4.7</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr"/>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>7.NS.A.2.C, 7.RP.3, 7.RP.A.2.B, 7.RP.A.2.D, 7.SP.7a</t>
+        </is>
+      </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>9.2.4.10 (MN-2022), 9.2.4.11 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.4 (MN-2022), 9.2.4.6 (MN-2022), 9.2.4.7 (MN-2022)</t>
+          <t>7.NS.A.2.C (CCSS-M), 7.RP.3 (CCSS-M), 7.RP.A.2.B (CCSS-M), 7.RP.A.2.D (CCSS-M), 7.SP.7a (CCSS-M), 9.2.4.10 (MN-2022), 9.2.4.11 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.4 (MN-2022), 9.2.4.6 (MN-2022), 9.2.4.7 (MN-2022)</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1172,15 +1242,19 @@
           <t>9.2.3.3, 9.2.4.1, 9.2.4.12, 9.2.4.15, 9.2.4.3</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr"/>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.A, 7.NS.A.2.A, 7.SP.6, 7.SP.7a, 7.SP.C.7.B</t>
+        </is>
+      </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>9.2.3.3 (MN-2022), 9.2.4.1 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.15 (MN-2022), 9.2.4.3 (MN-2022)</t>
+          <t>7.NS.A.1.A (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.SP.6 (CCSS-M), 7.SP.7a (CCSS-M), 7.SP.C.7.B (CCSS-M), 9.2.3.3 (MN-2022), 9.2.4.1 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.15 (MN-2022), 9.2.4.3 (MN-2022)</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1199,15 +1273,19 @@
           <t>9.2.3.9</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr"/>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.D</t>
+        </is>
+      </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>9.2.3.9 (MN-2022)</t>
+          <t>7.NS.A.1.D (CCSS-M), 9.2.3.9 (MN-2022)</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1226,15 +1304,19 @@
           <t>9.2.4.3</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr"/>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>7.NS.A.2.A</t>
+        </is>
+      </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>9.2.4.3 (MN-2022)</t>
+          <t>7.NS.A.2.A (CCSS-M), 9.2.4.3 (MN-2022)</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1270,15 +1352,19 @@
           <t>9.2.3.3, 9.2.4.12</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr"/>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>7.SP.7a, 7.SP.C.7.B</t>
+        </is>
+      </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>9.2.3.3 (MN-2022), 9.2.4.12 (MN-2022)</t>
+          <t>7.SP.7a (CCSS-M), 7.SP.C.7.B (CCSS-M), 9.2.3.3 (MN-2022), 9.2.4.12 (MN-2022)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1297,15 +1383,19 @@
           <t>9.2.3.4, 9.2.3.9</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr"/>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.D, 7.SP.C.7.A</t>
+        </is>
+      </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>9.2.3.4 (MN-2022), 9.2.3.9 (MN-2022)</t>
+          <t>7.NS.A.1.D (CCSS-M), 7.SP.C.7.A (CCSS-M), 9.2.3.4 (MN-2022), 9.2.3.9 (MN-2022)</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1324,15 +1414,19 @@
           <t>9.2.4.1, 9.2.4.12</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr"/>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.A, 7.SP.7a</t>
+        </is>
+      </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>9.2.4.1 (MN-2022), 9.2.4.12 (MN-2022)</t>
+          <t>7.NS.A.1.A (CCSS-M), 7.SP.7a (CCSS-M), 9.2.4.1 (MN-2022), 9.2.4.12 (MN-2022)</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1364,15 +1458,19 @@
           <t>9.2.4.8, 9.2.4.9</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr"/>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.C, 7.RP.A.2.C</t>
+        </is>
+      </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>9.2.4.8 (MN-2022), 9.2.4.9 (MN-2022)</t>
+          <t>7.NS.A.1.C (CCSS-M), 7.RP.A.2.C (CCSS-M), 9.2.4.8 (MN-2022), 9.2.4.9 (MN-2022)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1391,15 +1489,19 @@
           <t>9.1.2.1, 9.1.2.3, 9.1.2.5</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr"/>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>6.EE.A.4, 6.NS.3, Review skills needed for 6.NS.1</t>
+        </is>
+      </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>9.1.2.1 (MN-2022), 9.1.2.3 (MN-2022), 9.1.2.5 (MN-2022)</t>
+          <t>6.EE.A.4 (CCSS-M), 6.NS.3 (CCSS-M), 9.1.2.1 (MN-2022), 9.1.2.3 (MN-2022), 9.1.2.5 (MN-2022), Review skills needed for 6.NS.1 (CCSS-M)</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1418,15 +1520,19 @@
           <t>9.1.2.1</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr"/>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>6.EE.A.4</t>
+        </is>
+      </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>9.1.2.1 (MN-2022)</t>
+          <t>6.EE.A.4 (CCSS-M), 9.1.2.1 (MN-2022)</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1458,15 +1564,19 @@
           <t>9.2.3.4, 9.2.3.5</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>7.SP.C.7.A, Prep for 7.SP.C.8.A</t>
+        </is>
+      </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>9.2.3.4 (MN-2022), 9.2.3.5 (MN-2022)</t>
+          <t>7.SP.C.7.A (CCSS-M), 9.2.3.4 (MN-2022), 9.2.3.5 (MN-2022), Prep for 7.SP.C.8.A (CCSS-M)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1485,15 +1595,19 @@
           <t>9.2.3.5, 9.2.4.12, 9.2.4.8, 9.2.4.9</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.C, 7.RP.A.2.C, 7.SP.7a, Prep for 7.SP.C.8.A</t>
+        </is>
+      </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>9.2.3.5 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.8 (MN-2022), 9.2.4.9 (MN-2022)</t>
+          <t>7.NS.A.1.C (CCSS-M), 7.RP.A.2.C (CCSS-M), 7.SP.7a (CCSS-M), 9.2.3.5 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.8 (MN-2022), 9.2.4.9 (MN-2022), Prep for 7.SP.C.8.A (CCSS-M)</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1525,15 +1639,19 @@
           <t>9.2.3.3, 9.2.4.12, 9.3.6.6</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr"/>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>7.SP.7a, 7.SP.C.7.B, MP4</t>
+        </is>
+      </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>9.2.3.3 (MN-2022), 9.2.4.12 (MN-2022), 9.3.6.6 (MN-2022)</t>
+          <t>7.SP.7a (CCSS-M), 7.SP.C.7.B (CCSS-M), 9.2.3.3 (MN-2022), 9.2.4.12 (MN-2022), 9.3.6.6 (MN-2022), MP4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>

--- a/viewer/downloads/CCG_Alignment.xlsx
+++ b/viewer/downloads/CCG_Alignment.xlsx
@@ -62,7 +62,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -77,11 +77,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -125,7 +120,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,7 +492,7 @@
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
@@ -608,14 +602,10 @@
           <t>9.2.4.12, 9.2.4.6</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>7.RP.A.2.D, 7.SP.7a</t>
-        </is>
-      </c>
+      <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>7.RP.A.2.D (CCSS-M), 7.SP.7a (CCSS-M), 9.2.4.12 (MN-2022), 9.2.4.6 (MN-2022)</t>
+          <t>9.2.4.12 (MN-2022), 9.2.4.6 (MN-2022), 9.3.2.3 (MN-2007), 9.3.2.5 (MN-2007)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -643,14 +633,10 @@
           <t>9.2.4.1, 9.2.4.12, 9.2.4.13, 9.2.4.14</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.A, 7.SP.7a, 7.SP.7b, 7.SP.7c</t>
-        </is>
-      </c>
+      <c r="E8" s="7" t="inlineStr"/>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.1.A (CCSS-M), 7.SP.7a (CCSS-M), 7.SP.7b (CCSS-M), 7.SP.7c (CCSS-M), 9.2.4.1 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.13 (MN-2022), 9.2.4.14 (MN-2022)</t>
+          <t>9.2.4.1 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.13 (MN-2022), 9.2.4.14 (MN-2022), 9.3.2.5 (MN-2007), 9.3.3.1 (MN-2007), 9.3.3.2 (MN-2007), 9.3.4.6 (MN-2007)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -691,14 +677,10 @@
           <t>9.2.4.1, 9.2.4.12, 9.2.4.7</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.A, 7.RP.A.2.B, 7.SP.7a</t>
-        </is>
-      </c>
+      <c r="E10" s="7" t="inlineStr"/>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.1.A (CCSS-M), 7.RP.A.2.B (CCSS-M), 7.SP.7a (CCSS-M), 9.2.4.1 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.7 (MN-2022)</t>
+          <t>9.2.4.1 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.7 (MN-2022), 9.3.2.1 (MN-2007), 9.3.2.4 (MN-2007), 9.3.2.5 (MN-2007), 9.3.3.1 (MN-2007), 9.3.3.2 (MN-2007)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -726,14 +708,10 @@
           <t>9.2.3.6, 9.2.4.12</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>5.NF.A.1, 7.SP.7a</t>
-        </is>
-      </c>
+      <c r="E11" s="7" t="inlineStr"/>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>5.NF.A.1 (CCSS-M), 7.SP.7a (CCSS-M), 9.2.3.6 (MN-2022), 9.2.4.12 (MN-2022)</t>
+          <t>9.2.3.6 (MN-2022), 9.2.4.12 (MN-2022), 9.3.1.3 (MN-2007), 9.3.2.5 (MN-2007)</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -774,14 +752,10 @@
           <t>9.2.3.9</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.D</t>
-        </is>
-      </c>
+      <c r="E13" s="7" t="inlineStr"/>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.1.D (CCSS-M), 9.2.3.9 (MN-2022)</t>
+          <t>9.2.3.9 (MN-2022), 9.3.1.4 (MN-2007)</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -822,14 +796,10 @@
           <t>9.2.3.3, 9.2.3.8, 9.2.4.12</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>7.SP.7a, 7.SP.C.7.B, 7.SP.C.8.A</t>
-        </is>
-      </c>
+      <c r="E15" s="7" t="inlineStr"/>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>7.SP.7a (CCSS-M), 7.SP.C.7.B (CCSS-M), 7.SP.C.8.A (CCSS-M), 9.2.3.3 (MN-2022), 9.2.3.8 (MN-2022), 9.2.4.12 (MN-2022)</t>
+          <t>9.2.3.3 (MN-2022), 9.2.3.8 (MN-2022), 9.2.4.12 (MN-2022), 9.3.2.5 (MN-2007), 9.3.3.4 (MN-2007), 9.3.4.1 (MN-2007), 9.3.4.2 (MN-2007), 9.3.4.3 (MN-2007)</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -866,14 +836,10 @@
           <t>9.2.3.3, 9.2.3.8</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>7.SP.C.7.B, 7.SP.C.8.A</t>
-        </is>
-      </c>
+      <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>7.SP.C.7.B (CCSS-M), 7.SP.C.8.A (CCSS-M), 9.2.3.3 (MN-2022), 9.2.3.8 (MN-2022)</t>
+          <t>9.2.3.3 (MN-2022), 9.2.3.8 (MN-2022), 9.3.3.4 (MN-2007), 9.3.4.1 (MN-2007), 9.3.4.2 (MN-2007), 9.3.4.3 (MN-2007)</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -897,14 +863,10 @@
           <t>9.1.2.8, 9.2.3.2, 9.2.3.3</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>7.NS.A.2.D, 7.SP.C.7.B, 7.SP.C.8.C</t>
-        </is>
-      </c>
+      <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.2.D (CCSS-M), 7.SP.C.7.B (CCSS-M), 7.SP.C.8.C (CCSS-M), 9.1.2.8 (MN-2022), 9.2.3.2 (MN-2022), 9.2.3.3 (MN-2022)</t>
+          <t>9.1.2.8 (MN-2022), 9.2.3.2 (MN-2022), 9.2.3.3 (MN-2022), 9.3.3.4 (MN-2007), 9.3.3.5 (MN-2007), 9.3.4.2 (MN-2007), 9.3.4.3 (MN-2007), 9.4.3.8 (MN-2007)</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
@@ -928,14 +890,10 @@
           <t>9.2.3.2, 9.2.3.3</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>7.NS.A.2.D, 7.SP.C.7.B</t>
-        </is>
-      </c>
+      <c r="E19" s="7" t="inlineStr"/>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.2.D (CCSS-M), 7.SP.C.7.B (CCSS-M), 9.2.3.2 (MN-2022), 9.2.3.3 (MN-2022)</t>
+          <t>9.2.3.2 (MN-2022), 9.2.3.3 (MN-2022), 9.3.3.4 (MN-2007), 9.3.3.5 (MN-2007), 9.3.4.2 (MN-2007), 9.3.4.3 (MN-2007)</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -972,14 +930,10 @@
           <t>9.2.4.10, 9.2.4.4, 9.2.4.5, 9.2.4.7</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>7.NS.A.2.C, 7.RP.3, 7.RP.A.2.A, 7.RP.A.2.B</t>
-        </is>
-      </c>
+      <c r="E21" s="7" t="inlineStr"/>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.2.C (CCSS-M), 7.RP.3 (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M), 9.2.4.10 (MN-2022), 9.2.4.4 (MN-2022), 9.2.4.5 (MN-2022), 9.2.4.7 (MN-2022)</t>
+          <t>9.2.4.10 (MN-2022), 9.2.4.4 (MN-2022), 9.2.4.5 (MN-2022), 9.2.4.7 (MN-2022), 9.3.2.1 (MN-2007), 9.3.2.2 (MN-2007), 9.3.2.4 (MN-2007), 9.3.3.6 (MN-2007)</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -1003,14 +957,10 @@
           <t>9.2.3.1, 9.2.4.10</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>7.RP.3, 8.EE.C.7.B</t>
-        </is>
-      </c>
+      <c r="E22" s="7" t="inlineStr"/>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>7.RP.3 (CCSS-M), 8.EE.C.7.B (CCSS-M), 9.2.3.1 (MN-2022), 9.2.4.10 (MN-2022)</t>
+          <t>9.2.3.1 (MN-2022), 9.2.4.10 (MN-2022), 9.3.3.6 (MN-2007), 9.3.3.7 (MN-2007), 9.3.4.4 (MN-2007)</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
@@ -1051,14 +1001,10 @@
           <t>9.1.2.1, 9.1.2.2, 9.1.2.3, 9.1.2.4, 9.1.2.7</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>6.EE.A.2.C, 6.EE.A.4, 6.G.1, 6.RP.3c, Review skills needed for 6.NS.1</t>
-        </is>
-      </c>
+      <c r="E24" s="7" t="inlineStr"/>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>6.EE.A.2.C (CCSS-M), 6.EE.A.4 (CCSS-M), 6.G.1 (CCSS-M), 6.RP.3c (CCSS-M), 9.1.2.1 (MN-2022), 9.1.2.2 (MN-2022), 9.1.2.3 (MN-2022), 9.1.2.4 (MN-2022), 9.1.2.7 (MN-2022), Review skills needed for 6.NS.1 (CCSS-M)</t>
+          <t>9.1.2.1 (MN-2022), 9.1.2.2 (MN-2022), 9.1.2.3 (MN-2022), 9.1.2.4 (MN-2022), 9.1.2.7 (MN-2022), 9.4.3.1 (MN-2007), 9.4.3.2 (MN-2007), 9.4.3.3 (MN-2007), 9.4.3.5 (MN-2007), 9.4.3.6 (MN-2007), 9.4.3.7 (MN-2007)</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
@@ -1082,14 +1028,10 @@
           <t>9.2.4.15</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>7.SP.6</t>
-        </is>
-      </c>
+      <c r="E25" s="7" t="inlineStr"/>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>7.SP.6 (CCSS-M), 9.2.4.15 (MN-2022)</t>
+          <t>9.2.4.15 (MN-2022), 9.3.4.7 (MN-2007)</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -1113,14 +1055,10 @@
           <t>9.2.4.3, 9.2.4.4, 9.2.4.7</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>7.NS.A.2.A, 7.NS.A.2.C, 7.RP.A.2.B</t>
-        </is>
-      </c>
+      <c r="E26" s="7" t="inlineStr"/>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.2.A (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.RP.A.2.B (CCSS-M), 9.2.4.3 (MN-2022), 9.2.4.4 (MN-2022), 9.2.4.7 (MN-2022)</t>
+          <t>9.2.4.3 (MN-2022), 9.2.4.4 (MN-2022), 9.2.4.7 (MN-2022), 9.3.2.1 (MN-2007), 9.3.2.4 (MN-2007), 9.3.3.6 (MN-2007), 9.3.3.7 (MN-2007)</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -1144,14 +1082,10 @@
           <t>9.2.3.1</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.B</t>
-        </is>
-      </c>
+      <c r="E27" s="7" t="inlineStr"/>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>8.EE.C.7.B (CCSS-M), 9.2.3.1 (MN-2022)</t>
+          <t>9.2.3.1 (MN-2022), 9.3.3.7 (MN-2007), 9.3.4.4 (MN-2007)</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -1211,14 +1145,10 @@
           <t>9.2.4.10, 9.2.4.11, 9.2.4.12, 9.2.4.4, 9.2.4.6, 9.2.4.7</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>7.NS.A.2.C, 7.RP.3, 7.RP.A.2.B, 7.RP.A.2.D, 7.SP.7a</t>
-        </is>
-      </c>
+      <c r="E30" s="7" t="inlineStr"/>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.2.C (CCSS-M), 7.RP.3 (CCSS-M), 7.RP.A.2.B (CCSS-M), 7.RP.A.2.D (CCSS-M), 7.SP.7a (CCSS-M), 9.2.4.10 (MN-2022), 9.2.4.11 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.4 (MN-2022), 9.2.4.6 (MN-2022), 9.2.4.7 (MN-2022)</t>
+          <t>9.2.4.10 (MN-2022), 9.2.4.11 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.4 (MN-2022), 9.2.4.6 (MN-2022), 9.2.4.7 (MN-2022), 9.3.2.1 (MN-2007), 9.3.2.3 (MN-2007), 9.3.2.4 (MN-2007), 9.3.2.5 (MN-2007), 9.3.3.6 (MN-2007)</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -1242,14 +1172,10 @@
           <t>9.2.3.3, 9.2.4.1, 9.2.4.12, 9.2.4.15, 9.2.4.3</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.A, 7.NS.A.2.A, 7.SP.6, 7.SP.7a, 7.SP.C.7.B</t>
-        </is>
-      </c>
+      <c r="E31" s="7" t="inlineStr"/>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.1.A (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.SP.6 (CCSS-M), 7.SP.7a (CCSS-M), 7.SP.C.7.B (CCSS-M), 9.2.3.3 (MN-2022), 9.2.4.1 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.15 (MN-2022), 9.2.4.3 (MN-2022)</t>
+          <t>9.2.3.3 (MN-2022), 9.2.4.1 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.15 (MN-2022), 9.2.4.3 (MN-2022), 9.3.2.5 (MN-2007), 9.3.3.1 (MN-2007), 9.3.3.2 (MN-2007), 9.3.3.4 (MN-2007), 9.3.3.7 (MN-2007), 9.3.4.2 (MN-2007), 9.3.4.3 (MN-2007), 9.3.4.7 (MN-2007)</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -1273,14 +1199,10 @@
           <t>9.2.3.9</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.D</t>
-        </is>
-      </c>
+      <c r="E32" s="7" t="inlineStr"/>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.1.D (CCSS-M), 9.2.3.9 (MN-2022)</t>
+          <t>9.2.3.9 (MN-2022), 9.3.1.4 (MN-2007)</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -1304,14 +1226,10 @@
           <t>9.2.4.3</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>7.NS.A.2.A</t>
-        </is>
-      </c>
+      <c r="E33" s="7" t="inlineStr"/>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.2.A (CCSS-M), 9.2.4.3 (MN-2022)</t>
+          <t>9.2.4.3 (MN-2022), 9.3.3.7 (MN-2007)</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -1352,14 +1270,10 @@
           <t>9.2.3.3, 9.2.4.12</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>7.SP.7a, 7.SP.C.7.B</t>
-        </is>
-      </c>
+      <c r="E35" s="7" t="inlineStr"/>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>7.SP.7a (CCSS-M), 7.SP.C.7.B (CCSS-M), 9.2.3.3 (MN-2022), 9.2.4.12 (MN-2022)</t>
+          <t>9.2.3.3 (MN-2022), 9.2.4.12 (MN-2022), 9.3.2.5 (MN-2007), 9.3.3.4 (MN-2007), 9.3.4.2 (MN-2007), 9.3.4.3 (MN-2007)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -1383,14 +1297,10 @@
           <t>9.2.3.4, 9.2.3.9</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.D, 7.SP.C.7.A</t>
-        </is>
-      </c>
+      <c r="E36" s="7" t="inlineStr"/>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.1.D (CCSS-M), 7.SP.C.7.A (CCSS-M), 9.2.3.4 (MN-2022), 9.2.3.9 (MN-2022)</t>
+          <t>9.2.3.4 (MN-2022), 9.2.3.9 (MN-2022), 9.3.1.2 (MN-2007), 9.3.1.4 (MN-2007)</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -1414,14 +1324,10 @@
           <t>9.2.4.1, 9.2.4.12</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.A, 7.SP.7a</t>
-        </is>
-      </c>
+      <c r="E37" s="7" t="inlineStr"/>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.1.A (CCSS-M), 7.SP.7a (CCSS-M), 9.2.4.1 (MN-2022), 9.2.4.12 (MN-2022)</t>
+          <t>9.2.4.1 (MN-2022), 9.2.4.12 (MN-2022), 9.3.2.5 (MN-2007), 9.3.3.1 (MN-2007), 9.3.3.2 (MN-2007)</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -1458,14 +1364,10 @@
           <t>9.2.4.8, 9.2.4.9</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.C, 7.RP.A.2.C</t>
-        </is>
-      </c>
+      <c r="E39" s="7" t="inlineStr"/>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.1.C (CCSS-M), 7.RP.A.2.C (CCSS-M), 9.2.4.8 (MN-2022), 9.2.4.9 (MN-2022)</t>
+          <t>9.2.4.8 (MN-2022), 9.2.4.9 (MN-2022), 9.3.3.8 (MN-2007)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -1489,14 +1391,10 @@
           <t>9.1.2.1, 9.1.2.3, 9.1.2.5</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>6.EE.A.4, 6.NS.3, Review skills needed for 6.NS.1</t>
-        </is>
-      </c>
+      <c r="E40" s="7" t="inlineStr"/>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>6.EE.A.4 (CCSS-M), 6.NS.3 (CCSS-M), 9.1.2.1 (MN-2022), 9.1.2.3 (MN-2022), 9.1.2.5 (MN-2022), Review skills needed for 6.NS.1 (CCSS-M)</t>
+          <t>9.1.2.1 (MN-2022), 9.1.2.3 (MN-2022), 9.1.2.5 (MN-2022), 9.4.3.1 (MN-2007), 9.4.3.5 (MN-2007), 9.4.3.9 (MN-2007)</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -1520,14 +1418,10 @@
           <t>9.1.2.1</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>6.EE.A.4</t>
-        </is>
-      </c>
+      <c r="E41" s="7" t="inlineStr"/>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>6.EE.A.4 (CCSS-M), 9.1.2.1 (MN-2022)</t>
+          <t>9.1.2.1 (MN-2022), 9.4.3.1 (MN-2007)</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -1564,14 +1458,10 @@
           <t>9.2.3.4, 9.2.3.5</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>7.SP.C.7.A, Prep for 7.SP.C.8.A</t>
-        </is>
-      </c>
+      <c r="E43" s="7" t="inlineStr"/>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>7.SP.C.7.A (CCSS-M), 9.2.3.4 (MN-2022), 9.2.3.5 (MN-2022), Prep for 7.SP.C.8.A (CCSS-M)</t>
+          <t>9.2.3.4 (MN-2022), 9.2.3.5 (MN-2022), 9.3.1.1 (MN-2007), 9.3.1.2 (MN-2007)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -1595,14 +1485,10 @@
           <t>9.2.3.5, 9.2.4.12, 9.2.4.8, 9.2.4.9</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.C, 7.RP.A.2.C, 7.SP.7a, Prep for 7.SP.C.8.A</t>
-        </is>
-      </c>
+      <c r="E44" s="7" t="inlineStr"/>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.1.C (CCSS-M), 7.RP.A.2.C (CCSS-M), 7.SP.7a (CCSS-M), 9.2.3.5 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.8 (MN-2022), 9.2.4.9 (MN-2022), Prep for 7.SP.C.8.A (CCSS-M)</t>
+          <t>9.2.3.5 (MN-2022), 9.2.4.12 (MN-2022), 9.2.4.8 (MN-2022), 9.2.4.9 (MN-2022), 9.3.1.1 (MN-2007), 9.3.2.5 (MN-2007), 9.3.3.8 (MN-2007)</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -1639,14 +1525,10 @@
           <t>9.2.3.3, 9.2.4.12, 9.3.6.6</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t>7.SP.7a, 7.SP.C.7.B, MP4</t>
-        </is>
-      </c>
+      <c r="E46" s="7" t="inlineStr"/>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>7.SP.7a (CCSS-M), 7.SP.C.7.B (CCSS-M), 9.2.3.3 (MN-2022), 9.2.4.12 (MN-2022), 9.3.6.6 (MN-2022), MP4 (CCSS-M)</t>
+          <t>9.2.3.3 (MN-2022), 9.2.4.12 (MN-2022), 9.3.2.5 (MN-2007), 9.3.3.4 (MN-2007), 9.3.4.2 (MN-2007), 9.3.4.3 (MN-2007), 9.3.4.5 (MN-2007), 9.3.6.6 (MN-2022)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
